--- a/public/exports/29189803.xlsx
+++ b/public/exports/29189803.xlsx
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029496</t>
+          <t xml:space="preserve">200029500</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029499</t>
+          <t xml:space="preserve">200029500</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029498</t>
+          <t xml:space="preserve">200029500</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029498</t>
+          <t xml:space="preserve">200029500</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029498</t>
+          <t xml:space="preserve">200029500</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029499</t>
+          <t xml:space="preserve">200029500</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029498</t>
+          <t xml:space="preserve">200029500</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029498</t>
+          <t xml:space="preserve">200029500</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -13914,7 +13914,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567886</t>
+          <t xml:space="preserve">311567884</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567886</t>
+          <t xml:space="preserve">311567884</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567886</t>
+          <t xml:space="preserve">311567884</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567886</t>
+          <t xml:space="preserve">311567884</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582270</t>
+          <t xml:space="preserve">311582271</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582270</t>
+          <t xml:space="preserve">311582271</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -14934,7 +14934,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594112</t>
+          <t xml:space="preserve">311594113</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594112</t>
+          <t xml:space="preserve">311594113</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594112</t>
+          <t xml:space="preserve">311594113</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -21114,7 +21114,7 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t xml:space="preserve">311757995</t>
+          <t xml:space="preserve">311758142</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
@@ -21234,7 +21234,7 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759422</t>
+          <t xml:space="preserve">311759421</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
@@ -21474,7 +21474,7 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759970</t>
+          <t xml:space="preserve">311759943</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
@@ -21534,7 +21534,7 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759970</t>
+          <t xml:space="preserve">311759943</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
@@ -21594,7 +21594,7 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759952</t>
+          <t xml:space="preserve">311759943</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
@@ -22494,7 +22494,7 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t xml:space="preserve">311780697</t>
+          <t xml:space="preserve">311780599</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t xml:space="preserve">311780697</t>
+          <t xml:space="preserve">311780599</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
@@ -23154,7 +23154,7 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t xml:space="preserve">311802437</t>
+          <t xml:space="preserve">311802433</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
@@ -23214,7 +23214,7 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t xml:space="preserve">311802436</t>
+          <t xml:space="preserve">311802433</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
@@ -23274,7 +23274,7 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t xml:space="preserve">311802434</t>
+          <t xml:space="preserve">311802433</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
@@ -24174,7 +24174,7 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868068</t>
+          <t xml:space="preserve">311868109</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
@@ -26454,7 +26454,7 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t xml:space="preserve">311919931</t>
+          <t xml:space="preserve">311919928</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">

--- a/public/exports/29189803.xlsx
+++ b/public/exports/29189803.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L453"/>
+  <dimension ref="A1:M453"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2044,10 +2209,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2104,10 +2274,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2164,10 +2339,15 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2224,10 +2404,15 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2284,10 +2469,15 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2344,10 +2534,15 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2404,10 +2599,15 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2464,10 +2664,15 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2524,10 +2729,15 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2584,10 +2794,15 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2644,10 +2859,15 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2704,10 +2924,15 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2764,10 +2989,15 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2824,10 +3054,15 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2884,10 +3119,15 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2944,10 +3184,15 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3004,10 +3249,15 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3064,10 +3314,15 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3124,10 +3379,15 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3184,10 +3444,15 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3244,10 +3509,15 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3304,10 +3574,15 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3364,10 +3639,15 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3424,10 +3704,15 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3484,10 +3769,15 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3544,10 +3834,15 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3604,10 +3899,15 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3664,10 +3964,15 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3724,10 +4029,15 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3784,10 +4094,15 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3844,10 +4159,15 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3904,10 +4224,15 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3964,10 +4289,15 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4024,10 +4354,15 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4084,10 +4419,15 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4144,10 +4484,15 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4204,10 +4549,15 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4264,10 +4614,15 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4324,10 +4679,15 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4384,10 +4744,15 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4444,10 +4809,15 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4504,10 +4874,15 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4564,10 +4939,15 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4624,10 +5004,15 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4684,10 +5069,15 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4744,10 +5134,15 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4804,10 +5199,15 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4864,10 +5264,15 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4924,10 +5329,15 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4984,10 +5394,15 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5044,10 +5459,15 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5104,10 +5524,15 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5164,10 +5589,15 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5224,10 +5654,15 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5284,10 +5719,15 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5344,10 +5784,15 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5404,10 +5849,15 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5464,10 +5914,15 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5524,10 +5979,15 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5584,10 +6044,15 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5644,10 +6109,15 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5704,10 +6174,15 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5764,10 +6239,15 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5824,10 +6304,15 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5884,10 +6369,15 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5944,10 +6434,15 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6004,10 +6499,15 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6064,10 +6564,15 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6124,10 +6629,15 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6184,10 +6694,15 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6244,10 +6759,15 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6304,10 +6824,15 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6364,10 +6889,15 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6424,10 +6954,15 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6484,10 +7019,15 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6544,10 +7084,15 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6604,10 +7149,15 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6664,10 +7214,15 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6724,10 +7279,15 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6784,10 +7344,15 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6844,10 +7409,15 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-04-17</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="L115" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-04-17</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="L116" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-04-17</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-04-29</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="L118" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-04-29</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-04-29</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
+      <c r="L120" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-18</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
+      <c r="L121" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-07</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
+      <c r="L122" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-27</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
+      <c r="L123" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-28</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
+      <c r="L124" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-28</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
+      <c r="L125" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-28</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
+      <c r="L126" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr">
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-28</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
+      <c r="L127" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-28</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
+      <c r="L128" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-29</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
+      <c r="L129" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-29</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
+      <c r="L130" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
+      <c r="L131" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
+      <c r="L132" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
+      <c r="L133" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
+      <c r="L134" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
+      <c r="L135" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
+      <c r="L136" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
+      <c r="L137" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
+      <c r="L138" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr">
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
+      <c r="L139" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr">
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
+      <c r="L140" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr">
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
+      <c r="L141" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
+      <c r="L142" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
+      <c r="L143" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
+      <c r="L144" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
+      <c r="L145" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr">
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
+      <c r="L146" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr">
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
+      <c r="L147" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr">
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
+      <c r="L148" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-19</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
+      <c r="L149" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">Martin Jessen Rådg. ing. FRI</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-08</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
+      <c r="L150" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-17</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
+      <c r="L151" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr">
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-03-19</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
+      <c r="L152" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr">
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-03-19</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
+      <c r="L153" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr">
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-03-19</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
+      <c r="L154" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr">
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-03-19</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
+      <c r="L155" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr">
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-03-19</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
+      <c r="L156" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-03-19</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
+      <c r="L157" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-03-19</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
+      <c r="L158" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr">
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-03-19</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
+      <c r="L159" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr">
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-03-19</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
+      <c r="L160" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr">
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-03-19</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
+      <c r="L161" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-03-19</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
+      <c r="L162" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr">
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-04-26</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
+      <c r="L163" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-04-26</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
+      <c r="L164" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr">
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-04-26</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
+      <c r="L165" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr">
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-04-26</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
+      <c r="L166" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr">
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-05-04</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
+      <c r="L167" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr">
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-05-07</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
+      <c r="L168" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-05-07</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
+      <c r="L169" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr">
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-06-10</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
+      <c r="L170" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr">
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-06-10</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
+      <c r="L171" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr">
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-06-28</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
+      <c r="L172" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr">
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Sydvestjylland</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-01</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
+      <c r="L173" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr">
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-27</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
+      <c r="L174" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-27</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
+      <c r="L175" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-27</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
+      <c r="L176" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr">
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-28</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
+      <c r="L177" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr">
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-28</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
+      <c r="L178" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr">
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-28</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
+      <c r="L179" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr">
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-07-07</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
+      <c r="L180" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr">
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-17</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
+      <c r="L181" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr">
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-17</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
+      <c r="L182" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-03-26</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
+      <c r="L183" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr">
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-05-11</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
+      <c r="L184" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr">
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-08-16</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
+      <c r="L185" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr">
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-10-18</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
+      <c r="L186" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr">
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-01-04</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
+      <c r="L187" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr">
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-03-06</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
+      <c r="L188" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr">
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve">JOH Projekterende Rådgiver</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-06-11</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
+      <c r="L189" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L189" t="inlineStr">
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Center Sydvestjylland</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
+      <c r="L190" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L190" t="inlineStr">
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Center Sydvestjylland</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-19</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
+      <c r="L191" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr">
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ankersen IVS</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-23</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
+      <c r="L192" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr">
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
+      <c r="L193" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr">
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Center Sydvestjylland</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-03</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
+      <c r="L194" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L194" t="inlineStr">
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Center Sydvestjylland</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-05</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
+      <c r="L195" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr">
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Center Sydvestjylland</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-22</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
+      <c r="L196" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr">
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-08</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
+      <c r="L197" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr">
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-08</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
+      <c r="L198" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr">
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-08</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
+      <c r="L199" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr">
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-19</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
+      <c r="L200" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr">
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12059,15 +13059,20 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-19</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
+      <c r="L201" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr">
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12119,15 +13124,20 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vh-consult</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-24</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
+      <c r="L202" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr">
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12179,15 +13189,20 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">PAARUP arkitekter</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-29</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
+      <c r="L203" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L203" t="inlineStr">
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve">Arkitektfirmaet Byg &amp; Bo ApS</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-07-03</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
+      <c r="L204" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr">
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-08</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
+      <c r="L205" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr">
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-08</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
+      <c r="L206" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr">
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12419,15 +13449,20 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-27</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
+      <c r="L207" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr">
+      <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12479,15 +13514,20 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-14</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
+      <c r="L208" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr">
+      <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12539,15 +13579,20 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-18</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
+      <c r="L209" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr">
+      <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12599,15 +13644,20 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-14</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
+      <c r="L210" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr">
+      <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12659,15 +13709,20 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-14</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
+      <c r="L211" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr">
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12719,15 +13774,20 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-14</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
+      <c r="L212" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr">
+      <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12779,15 +13839,20 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-14</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
+      <c r="L213" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr">
+      <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12839,15 +13904,20 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-14</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
+      <c r="L214" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr">
+      <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12899,15 +13969,20 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-18</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
+      <c r="L215" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr">
+      <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12959,15 +14034,20 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-14</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
+      <c r="L216" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr">
+      <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13019,15 +14099,20 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-14</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
+      <c r="L217" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr">
+      <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13079,15 +14164,20 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-14</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
+      <c r="L218" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L218" t="inlineStr">
+      <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13139,15 +14229,20 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-14</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
+      <c r="L219" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr">
+      <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13199,15 +14294,20 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-14</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
+      <c r="L220" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L220" t="inlineStr">
+      <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13259,15 +14359,20 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-14</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
+      <c r="L221" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L221" t="inlineStr">
+      <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13319,15 +14424,20 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-14</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
+      <c r="L222" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L222" t="inlineStr">
+      <c r="M222" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13379,15 +14489,20 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-14</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
+      <c r="L223" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr">
+      <c r="M223" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13439,15 +14554,20 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-14</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
+      <c r="L224" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr">
+      <c r="M224" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13499,15 +14619,20 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-14</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
+      <c r="L225" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L225" t="inlineStr">
+      <c r="M225" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13559,15 +14684,20 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-14</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
+      <c r="L226" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr">
+      <c r="M226" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13619,15 +14749,20 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-14</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
+      <c r="L227" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L227" t="inlineStr">
+      <c r="M227" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13679,15 +14814,20 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-14</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
+      <c r="L228" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr">
+      <c r="M228" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13739,15 +14879,20 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-14</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
+      <c r="L229" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L229" t="inlineStr">
+      <c r="M229" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13799,15 +14944,20 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-14</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
+      <c r="L230" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L230" t="inlineStr">
+      <c r="M230" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13859,15 +15009,20 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-14</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
+      <c r="L231" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L231" t="inlineStr">
+      <c r="M231" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13919,15 +15074,20 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-14</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
+      <c r="L232" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L232" t="inlineStr">
+      <c r="M232" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13979,15 +15139,20 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-14</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
+      <c r="L233" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L233" t="inlineStr">
+      <c r="M233" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14039,15 +15204,20 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-14</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr">
+      <c r="L234" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L234" t="inlineStr">
+      <c r="M234" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14099,15 +15269,20 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-14</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
+      <c r="L235" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L235" t="inlineStr">
+      <c r="M235" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14159,15 +15334,20 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-14</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
+      <c r="L236" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L236" t="inlineStr">
+      <c r="M236" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14219,15 +15399,20 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-14</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
+      <c r="L237" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L237" t="inlineStr">
+      <c r="M237" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14279,15 +15464,20 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-14</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
+      <c r="L238" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L238" t="inlineStr">
+      <c r="M238" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14339,15 +15529,20 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-14</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
+      <c r="L239" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L239" t="inlineStr">
+      <c r="M239" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14399,15 +15594,20 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-03</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
+      <c r="L240" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L240" t="inlineStr">
+      <c r="M240" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14459,15 +15659,20 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-03</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr">
+      <c r="L241" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L241" t="inlineStr">
+      <c r="M241" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14519,15 +15724,20 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-03</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
+      <c r="L242" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L242" t="inlineStr">
+      <c r="M242" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14579,15 +15789,20 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-03</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
+      <c r="L243" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L243" t="inlineStr">
+      <c r="M243" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14639,15 +15854,20 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-03</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr">
+      <c r="L244" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L244" t="inlineStr">
+      <c r="M244" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14699,15 +15919,20 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-10</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr">
+      <c r="L245" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L245" t="inlineStr">
+      <c r="M245" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14759,15 +15984,20 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-10</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
+      <c r="L246" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L246" t="inlineStr">
+      <c r="M246" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14819,15 +16049,20 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-21</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr">
+      <c r="L247" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L247" t="inlineStr">
+      <c r="M247" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14879,15 +16114,20 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-21</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr">
+      <c r="L248" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L248" t="inlineStr">
+      <c r="M248" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14939,15 +16179,20 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-21</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr">
+      <c r="L249" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L249" t="inlineStr">
+      <c r="M249" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14999,15 +16244,20 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-21</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr">
+      <c r="L250" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L250" t="inlineStr">
+      <c r="M250" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15059,15 +16309,20 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-21</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
+      <c r="L251" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr">
+      <c r="M251" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15119,15 +16374,20 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-21</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr">
+      <c r="L252" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L252" t="inlineStr">
+      <c r="M252" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15179,15 +16439,20 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-29</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr">
+      <c r="L253" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L253" t="inlineStr">
+      <c r="M253" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15239,15 +16504,20 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-04</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr">
+      <c r="L254" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L254" t="inlineStr">
+      <c r="M254" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15299,15 +16569,20 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-04</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr">
+      <c r="L255" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L255" t="inlineStr">
+      <c r="M255" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15359,15 +16634,20 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr">
+      <c r="L256" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L256" t="inlineStr">
+      <c r="M256" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15419,15 +16699,20 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr">
+      <c r="L257" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L257" t="inlineStr">
+      <c r="M257" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15479,15 +16764,20 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr">
+      <c r="L258" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L258" t="inlineStr">
+      <c r="M258" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15539,15 +16829,20 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr">
+      <c r="L259" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L259" t="inlineStr">
+      <c r="M259" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15599,15 +16894,20 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
+      <c r="L260" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L260" t="inlineStr">
+      <c r="M260" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15659,15 +16959,20 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr">
+      <c r="L261" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L261" t="inlineStr">
+      <c r="M261" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15719,15 +17024,20 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr">
+      <c r="L262" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L262" t="inlineStr">
+      <c r="M262" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15779,15 +17089,20 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
+      <c r="L263" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L263" t="inlineStr">
+      <c r="M263" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15839,15 +17154,20 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr">
+      <c r="L264" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L264" t="inlineStr">
+      <c r="M264" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15899,15 +17219,20 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-25</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr">
+      <c r="L265" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L265" t="inlineStr">
+      <c r="M265" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15959,15 +17284,20 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-25</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr">
+      <c r="L266" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L266" t="inlineStr">
+      <c r="M266" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16019,15 +17349,20 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-01</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr">
+      <c r="L267" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L267" t="inlineStr">
+      <c r="M267" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16079,15 +17414,20 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-01</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr">
+      <c r="L268" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L268" t="inlineStr">
+      <c r="M268" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16139,15 +17479,20 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-01</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr">
+      <c r="L269" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L269" t="inlineStr">
+      <c r="M269" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16199,15 +17544,20 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-01</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr">
+      <c r="L270" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L270" t="inlineStr">
+      <c r="M270" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16259,15 +17609,20 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-05</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr">
+      <c r="L271" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L271" t="inlineStr">
+      <c r="M271" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16319,15 +17674,20 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-05</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr">
+      <c r="L272" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L272" t="inlineStr">
+      <c r="M272" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16379,15 +17739,20 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-05</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr">
+      <c r="L273" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L273" t="inlineStr">
+      <c r="M273" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16439,15 +17804,20 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-11</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr">
+      <c r="L274" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L274" t="inlineStr">
+      <c r="M274" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16499,15 +17869,20 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-11</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr">
+      <c r="L275" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L275" t="inlineStr">
+      <c r="M275" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16559,15 +17934,20 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-11</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr">
+      <c r="L276" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L276" t="inlineStr">
+      <c r="M276" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16619,15 +17999,20 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-11</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr">
+      <c r="L277" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L277" t="inlineStr">
+      <c r="M277" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16679,15 +18064,20 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-11</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr">
+      <c r="L278" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L278" t="inlineStr">
+      <c r="M278" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16739,15 +18129,20 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-11</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr">
+      <c r="L279" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L279" t="inlineStr">
+      <c r="M279" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16799,15 +18194,20 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-11</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr">
+      <c r="L280" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L280" t="inlineStr">
+      <c r="M280" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16859,15 +18259,20 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-11</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr">
+      <c r="L281" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L281" t="inlineStr">
+      <c r="M281" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16919,15 +18324,20 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-11</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr">
+      <c r="L282" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L282" t="inlineStr">
+      <c r="M282" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16979,15 +18389,20 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-11</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr">
+      <c r="L283" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L283" t="inlineStr">
+      <c r="M283" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17039,15 +18454,20 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-11</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr">
+      <c r="L284" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L284" t="inlineStr">
+      <c r="M284" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17099,15 +18519,20 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-11</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr">
+      <c r="L285" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L285" t="inlineStr">
+      <c r="M285" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17159,15 +18584,20 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-11</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr">
+      <c r="L286" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L286" t="inlineStr">
+      <c r="M286" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17219,15 +18649,20 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-11</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr">
+      <c r="L287" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L287" t="inlineStr">
+      <c r="M287" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17279,15 +18714,20 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-11</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr">
+      <c r="L288" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L288" t="inlineStr">
+      <c r="M288" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17339,15 +18779,20 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-11</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr">
+      <c r="L289" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L289" t="inlineStr">
+      <c r="M289" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17399,15 +18844,20 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-08</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr">
+      <c r="L290" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L290" t="inlineStr">
+      <c r="M290" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17459,15 +18909,20 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-08</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr">
+      <c r="L291" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L291" t="inlineStr">
+      <c r="M291" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17519,15 +18974,20 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-08</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr">
+      <c r="L292" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L292" t="inlineStr">
+      <c r="M292" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17579,15 +19039,20 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-08</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr">
+      <c r="L293" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L293" t="inlineStr">
+      <c r="M293" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17639,15 +19104,20 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-08</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr">
+      <c r="L294" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L294" t="inlineStr">
+      <c r="M294" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17699,15 +19169,20 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-08</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr">
+      <c r="L295" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L295" t="inlineStr">
+      <c r="M295" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17759,15 +19234,20 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-08</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr">
+      <c r="L296" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L296" t="inlineStr">
+      <c r="M296" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17819,15 +19299,20 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-08</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr">
+      <c r="L297" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L297" t="inlineStr">
+      <c r="M297" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17879,15 +19364,20 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-06</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr">
+      <c r="L298" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L298" t="inlineStr">
+      <c r="M298" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17939,15 +19429,20 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-06</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr">
+      <c r="L299" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L299" t="inlineStr">
+      <c r="M299" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17999,15 +19494,20 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-06</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr">
+      <c r="L300" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L300" t="inlineStr">
+      <c r="M300" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18059,15 +19559,20 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr">
+      <c r="L301" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L301" t="inlineStr">
+      <c r="M301" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18119,15 +19624,20 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-13</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr">
+      <c r="L302" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L302" t="inlineStr">
+      <c r="M302" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18179,15 +19689,20 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-13</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr">
+      <c r="L303" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L303" t="inlineStr">
+      <c r="M303" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18239,15 +19754,20 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-13</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr">
+      <c r="L304" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L304" t="inlineStr">
+      <c r="M304" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18299,15 +19819,20 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-13</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr">
+      <c r="L305" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L305" t="inlineStr">
+      <c r="M305" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18359,15 +19884,20 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-13</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr">
+      <c r="L306" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L306" t="inlineStr">
+      <c r="M306" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18419,15 +19949,20 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr">
+      <c r="L307" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L307" t="inlineStr">
+      <c r="M307" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18479,15 +20014,20 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr">
+      <c r="L308" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L308" t="inlineStr">
+      <c r="M308" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18539,15 +20079,20 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-13</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr">
+      <c r="L309" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L309" t="inlineStr">
+      <c r="M309" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18599,15 +20144,20 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr">
+      <c r="L310" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L310" t="inlineStr">
+      <c r="M310" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18659,15 +20209,20 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr">
+      <c r="L311" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L311" t="inlineStr">
+      <c r="M311" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18719,15 +20274,20 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr">
+      <c r="L312" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L312" t="inlineStr">
+      <c r="M312" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18779,15 +20339,20 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr">
+      <c r="L313" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L313" t="inlineStr">
+      <c r="M313" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18839,15 +20404,20 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr">
+      <c r="L314" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L314" t="inlineStr">
+      <c r="M314" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18899,15 +20469,20 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr">
+      <c r="L315" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L315" t="inlineStr">
+      <c r="M315" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18959,15 +20534,20 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr">
+      <c r="L316" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L316" t="inlineStr">
+      <c r="M316" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19019,15 +20599,20 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-30</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr">
+      <c r="L317" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L317" t="inlineStr">
+      <c r="M317" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19079,15 +20664,20 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-30</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr">
+      <c r="L318" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L318" t="inlineStr">
+      <c r="M318" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19139,15 +20729,20 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-30</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr">
+      <c r="L319" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L319" t="inlineStr">
+      <c r="M319" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19199,15 +20794,20 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-30</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr">
+      <c r="L320" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L320" t="inlineStr">
+      <c r="M320" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19259,15 +20859,20 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-30</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr">
+      <c r="L321" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L321" t="inlineStr">
+      <c r="M321" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19319,15 +20924,20 @@
       </c>
       <c r="J322" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-30</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr">
+      <c r="L322" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L322" t="inlineStr">
+      <c r="M322" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19379,15 +20989,20 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-13</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr">
+      <c r="L323" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L323" t="inlineStr">
+      <c r="M323" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19439,15 +21054,20 @@
       </c>
       <c r="J324" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-07</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr">
+      <c r="L324" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L324" t="inlineStr">
+      <c r="M324" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19499,15 +21119,20 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-25</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr">
+      <c r="L325" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L325" t="inlineStr">
+      <c r="M325" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19559,15 +21184,20 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-25</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr">
+      <c r="L326" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L326" t="inlineStr">
+      <c r="M326" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19619,15 +21249,20 @@
       </c>
       <c r="J327" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-25</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr">
+      <c r="L327" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L327" t="inlineStr">
+      <c r="M327" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19679,15 +21314,20 @@
       </c>
       <c r="J328" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-25</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr">
+      <c r="L328" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L328" t="inlineStr">
+      <c r="M328" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19739,15 +21379,20 @@
       </c>
       <c r="J329" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-26</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr">
+      <c r="L329" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L329" t="inlineStr">
+      <c r="M329" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19799,15 +21444,20 @@
       </c>
       <c r="J330" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-26</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr">
+      <c r="L330" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L330" t="inlineStr">
+      <c r="M330" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19859,15 +21509,20 @@
       </c>
       <c r="J331" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-26</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr">
+      <c r="L331" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L331" t="inlineStr">
+      <c r="M331" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19919,15 +21574,20 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-26</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr">
+      <c r="L332" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L332" t="inlineStr">
+      <c r="M332" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19979,15 +21639,20 @@
       </c>
       <c r="J333" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-26</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr">
+      <c r="L333" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L333" t="inlineStr">
+      <c r="M333" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20039,15 +21704,20 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-26</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr">
+      <c r="L334" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L334" t="inlineStr">
+      <c r="M334" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20099,15 +21769,20 @@
       </c>
       <c r="J335" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-26</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr">
+      <c r="L335" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L335" t="inlineStr">
+      <c r="M335" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20159,15 +21834,20 @@
       </c>
       <c r="J336" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-26</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr">
+      <c r="L336" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L336" t="inlineStr">
+      <c r="M336" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20219,15 +21899,20 @@
       </c>
       <c r="J337" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITA Ingeniører</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-26</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr">
+      <c r="L337" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L337" t="inlineStr">
+      <c r="M337" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20279,15 +21964,20 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-27</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr">
+      <c r="L338" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L338" t="inlineStr">
+      <c r="M338" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20339,15 +22029,20 @@
       </c>
       <c r="J339" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-30</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr">
+      <c r="L339" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L339" t="inlineStr">
+      <c r="M339" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20399,15 +22094,20 @@
       </c>
       <c r="J340" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-25</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr">
+      <c r="L340" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L340" t="inlineStr">
+      <c r="M340" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20459,15 +22159,20 @@
       </c>
       <c r="J341" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-26</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr">
+      <c r="L341" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L341" t="inlineStr">
+      <c r="M341" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20519,15 +22224,20 @@
       </c>
       <c r="J342" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-26</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr">
+      <c r="L342" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L342" t="inlineStr">
+      <c r="M342" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20579,15 +22289,20 @@
       </c>
       <c r="J343" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-26</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr">
+      <c r="L343" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L343" t="inlineStr">
+      <c r="M343" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20639,15 +22354,20 @@
       </c>
       <c r="J344" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-26</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr">
+      <c r="L344" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L344" t="inlineStr">
+      <c r="M344" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20699,15 +22419,20 @@
       </c>
       <c r="J345" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-26</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr">
+      <c r="L345" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L345" t="inlineStr">
+      <c r="M345" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20759,15 +22484,20 @@
       </c>
       <c r="J346" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-04-03</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr">
+      <c r="L346" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L346" t="inlineStr">
+      <c r="M346" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20819,15 +22549,20 @@
       </c>
       <c r="J347" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-04-03</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr">
+      <c r="L347" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L347" t="inlineStr">
+      <c r="M347" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20879,15 +22614,20 @@
       </c>
       <c r="J348" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-04-16</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr">
+      <c r="L348" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L348" t="inlineStr">
+      <c r="M348" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20939,15 +22679,20 @@
       </c>
       <c r="J349" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-04-16</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr">
+      <c r="L349" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L349" t="inlineStr">
+      <c r="M349" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20999,15 +22744,20 @@
       </c>
       <c r="J350" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-04-24</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr">
+      <c r="L350" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L350" t="inlineStr">
+      <c r="M350" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -21059,15 +22809,20 @@
       </c>
       <c r="J351" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-06</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr">
+      <c r="L351" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L351" t="inlineStr">
+      <c r="M351" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -21119,15 +22874,20 @@
       </c>
       <c r="J352" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-08</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr">
+      <c r="L352" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L352" t="inlineStr">
+      <c r="M352" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -21179,15 +22939,20 @@
       </c>
       <c r="J353" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-13</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr">
+      <c r="L353" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L353" t="inlineStr">
+      <c r="M353" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -21239,15 +23004,20 @@
       </c>
       <c r="J354" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-15</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr">
+      <c r="L354" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L354" t="inlineStr">
+      <c r="M354" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -21299,15 +23069,20 @@
       </c>
       <c r="J355" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-15</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr">
+      <c r="L355" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L355" t="inlineStr">
+      <c r="M355" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -21359,15 +23134,20 @@
       </c>
       <c r="J356" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-15</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr">
+      <c r="L356" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L356" t="inlineStr">
+      <c r="M356" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -21419,15 +23199,20 @@
       </c>
       <c r="J357" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-15</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr">
+      <c r="L357" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L357" t="inlineStr">
+      <c r="M357" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -21479,15 +23264,20 @@
       </c>
       <c r="J358" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-16</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr">
+      <c r="L358" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L358" t="inlineStr">
+      <c r="M358" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -21539,15 +23329,20 @@
       </c>
       <c r="J359" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-16</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr">
+      <c r="L359" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L359" t="inlineStr">
+      <c r="M359" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -21599,15 +23394,20 @@
       </c>
       <c r="J360" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-16</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr">
+      <c r="L360" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L360" t="inlineStr">
+      <c r="M360" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -21659,15 +23459,20 @@
       </c>
       <c r="J361" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-27</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr">
+      <c r="L361" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L361" t="inlineStr">
+      <c r="M361" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -21719,15 +23524,20 @@
       </c>
       <c r="J362" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-27</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr">
+      <c r="L362" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L362" t="inlineStr">
+      <c r="M362" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -21779,15 +23589,20 @@
       </c>
       <c r="J363" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-06</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr">
+      <c r="L363" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L363" t="inlineStr">
+      <c r="M363" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -21839,15 +23654,20 @@
       </c>
       <c r="J364" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-10</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr">
+      <c r="L364" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L364" t="inlineStr">
+      <c r="M364" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -21899,15 +23719,20 @@
       </c>
       <c r="J365" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-12</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr">
+      <c r="L365" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L365" t="inlineStr">
+      <c r="M365" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -21959,15 +23784,20 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
+          <t xml:space="preserve">STD Klima og Byggeri</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-15</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr">
+      <c r="L366" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L366" t="inlineStr">
+      <c r="M366" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -22019,15 +23849,20 @@
       </c>
       <c r="J367" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-26</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr">
+      <c r="L367" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L367" t="inlineStr">
+      <c r="M367" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -22079,15 +23914,20 @@
       </c>
       <c r="J368" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-07-09</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr">
+      <c r="L368" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L368" t="inlineStr">
+      <c r="M368" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -22139,15 +23979,20 @@
       </c>
       <c r="J369" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-07-10</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr">
+      <c r="L369" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L369" t="inlineStr">
+      <c r="M369" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -22199,15 +24044,20 @@
       </c>
       <c r="J370" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-07-10</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr">
+      <c r="L370" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L370" t="inlineStr">
+      <c r="M370" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -22259,15 +24109,20 @@
       </c>
       <c r="J371" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-14</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr">
+      <c r="L371" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L371" t="inlineStr">
+      <c r="M371" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -22319,15 +24174,20 @@
       </c>
       <c r="J372" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-14</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr">
+      <c r="L372" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L372" t="inlineStr">
+      <c r="M372" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -22379,15 +24239,20 @@
       </c>
       <c r="J373" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-14</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr">
+      <c r="L373" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L373" t="inlineStr">
+      <c r="M373" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -22439,15 +24304,20 @@
       </c>
       <c r="J374" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr">
+      <c r="L374" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L374" t="inlineStr">
+      <c r="M374" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -22499,15 +24369,20 @@
       </c>
       <c r="J375" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr">
+      <c r="L375" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L375" t="inlineStr">
+      <c r="M375" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -22559,15 +24434,20 @@
       </c>
       <c r="J376" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr">
+      <c r="L376" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L376" t="inlineStr">
+      <c r="M376" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -22619,15 +24499,20 @@
       </c>
       <c r="J377" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr">
+      <c r="L377" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L377" t="inlineStr">
+      <c r="M377" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -22679,15 +24564,20 @@
       </c>
       <c r="J378" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr">
+      <c r="L378" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L378" t="inlineStr">
+      <c r="M378" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -22739,15 +24629,20 @@
       </c>
       <c r="J379" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr">
+      <c r="L379" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L379" t="inlineStr">
+      <c r="M379" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -22799,15 +24694,20 @@
       </c>
       <c r="J380" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-30</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr">
+      <c r="L380" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L380" t="inlineStr">
+      <c r="M380" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -22859,15 +24759,20 @@
       </c>
       <c r="J381" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-11</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr">
+      <c r="L381" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L381" t="inlineStr">
+      <c r="M381" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -22919,15 +24824,20 @@
       </c>
       <c r="J382" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-11</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr">
+      <c r="L382" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L382" t="inlineStr">
+      <c r="M382" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -22979,15 +24889,20 @@
       </c>
       <c r="J383" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-11</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr">
+      <c r="L383" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L383" t="inlineStr">
+      <c r="M383" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -23039,15 +24954,20 @@
       </c>
       <c r="J384" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-11</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr">
+      <c r="L384" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L384" t="inlineStr">
+      <c r="M384" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -23099,15 +25019,20 @@
       </c>
       <c r="J385" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-11</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr">
+      <c r="L385" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L385" t="inlineStr">
+      <c r="M385" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -23159,15 +25084,20 @@
       </c>
       <c r="J386" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-13</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr">
+      <c r="L386" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L386" t="inlineStr">
+      <c r="M386" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -23219,15 +25149,20 @@
       </c>
       <c r="J387" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-13</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr">
+      <c r="L387" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L387" t="inlineStr">
+      <c r="M387" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -23279,15 +25214,20 @@
       </c>
       <c r="J388" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-13</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr">
+      <c r="L388" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L388" t="inlineStr">
+      <c r="M388" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -23339,15 +25279,20 @@
       </c>
       <c r="J389" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr">
+      <c r="L389" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L389" t="inlineStr">
+      <c r="M389" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -23399,15 +25344,20 @@
       </c>
       <c r="J390" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-12</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr">
+      <c r="L390" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L390" t="inlineStr">
+      <c r="M390" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -23459,15 +25409,20 @@
       </c>
       <c r="J391" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-23</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr">
+      <c r="L391" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L391" t="inlineStr">
+      <c r="M391" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -23519,15 +25474,20 @@
       </c>
       <c r="J392" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-23</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr">
+      <c r="L392" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L392" t="inlineStr">
+      <c r="M392" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -23579,15 +25539,20 @@
       </c>
       <c r="J393" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-05</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr">
+      <c r="L393" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L393" t="inlineStr">
+      <c r="M393" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -23639,15 +25604,20 @@
       </c>
       <c r="J394" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-05</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr">
+      <c r="L394" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L394" t="inlineStr">
+      <c r="M394" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -23699,15 +25669,20 @@
       </c>
       <c r="J395" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-14</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr">
+      <c r="L395" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L395" t="inlineStr">
+      <c r="M395" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -23759,15 +25734,20 @@
       </c>
       <c r="J396" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-18</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr">
+      <c r="L396" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L396" t="inlineStr">
+      <c r="M396" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -23819,15 +25799,20 @@
       </c>
       <c r="J397" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-25</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr">
+      <c r="L397" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L397" t="inlineStr">
+      <c r="M397" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -23879,15 +25864,20 @@
       </c>
       <c r="J398" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-01</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr">
+      <c r="L398" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L398" t="inlineStr">
+      <c r="M398" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -23939,15 +25929,20 @@
       </c>
       <c r="J399" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-03</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr">
+      <c r="L399" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L399" t="inlineStr">
+      <c r="M399" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -23999,15 +25994,20 @@
       </c>
       <c r="J400" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-04</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr">
+      <c r="L400" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L400" t="inlineStr">
+      <c r="M400" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -24059,15 +26059,20 @@
       </c>
       <c r="J401" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-17</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr">
+      <c r="L401" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L401" t="inlineStr">
+      <c r="M401" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -24119,15 +26124,20 @@
       </c>
       <c r="J402" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-06</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr">
+      <c r="L402" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L402" t="inlineStr">
+      <c r="M402" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -24179,15 +26189,20 @@
       </c>
       <c r="J403" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-13</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr">
+      <c r="L403" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L403" t="inlineStr">
+      <c r="M403" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -24239,15 +26254,20 @@
       </c>
       <c r="J404" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr">
+      <c r="L404" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L404" t="inlineStr">
+      <c r="M404" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -24299,15 +26319,20 @@
       </c>
       <c r="J405" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-21</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr">
+      <c r="L405" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L405" t="inlineStr">
+      <c r="M405" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -24359,15 +26384,20 @@
       </c>
       <c r="J406" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-21</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr">
+      <c r="L406" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L406" t="inlineStr">
+      <c r="M406" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -24419,15 +26449,20 @@
       </c>
       <c r="J407" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-28</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr">
+      <c r="L407" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L407" t="inlineStr">
+      <c r="M407" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -24479,15 +26514,20 @@
       </c>
       <c r="J408" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-28</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr">
+      <c r="L408" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L408" t="inlineStr">
+      <c r="M408" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -24539,15 +26579,20 @@
       </c>
       <c r="J409" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-01</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr">
+      <c r="L409" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L409" t="inlineStr">
+      <c r="M409" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -24599,15 +26644,20 @@
       </c>
       <c r="J410" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-17</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr">
+      <c r="L410" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L410" t="inlineStr">
+      <c r="M410" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -24659,15 +26709,20 @@
       </c>
       <c r="J411" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-17</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr">
+      <c r="L411" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L411" t="inlineStr">
+      <c r="M411" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -24719,15 +26774,20 @@
       </c>
       <c r="J412" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr">
+      <c r="L412" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L412" t="inlineStr">
+      <c r="M412" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -24779,15 +26839,20 @@
       </c>
       <c r="J413" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-14</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr">
+      <c r="L413" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L413" t="inlineStr">
+      <c r="M413" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -24839,15 +26904,20 @@
       </c>
       <c r="J414" t="inlineStr">
         <is>
+          <t xml:space="preserve">STD Klima og Byggeri</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-15</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr">
+      <c r="L414" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L414" t="inlineStr">
+      <c r="M414" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -24899,15 +26969,20 @@
       </c>
       <c r="J415" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-17</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr">
+      <c r="L415" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L415" t="inlineStr">
+      <c r="M415" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -24959,15 +27034,20 @@
       </c>
       <c r="J416" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-22</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr">
+      <c r="L416" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L416" t="inlineStr">
+      <c r="M416" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -25019,15 +27099,20 @@
       </c>
       <c r="J417" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-29</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr">
+      <c r="L417" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L417" t="inlineStr">
+      <c r="M417" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -25079,15 +27164,20 @@
       </c>
       <c r="J418" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr">
+      <c r="L418" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L418" t="inlineStr">
+      <c r="M418" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -25139,15 +27229,20 @@
       </c>
       <c r="J419" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr">
+      <c r="L419" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L419" t="inlineStr">
+      <c r="M419" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -25199,15 +27294,20 @@
       </c>
       <c r="J420" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr">
+      <c r="L420" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L420" t="inlineStr">
+      <c r="M420" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -25259,15 +27359,20 @@
       </c>
       <c r="J421" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr">
+      <c r="L421" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L421" t="inlineStr">
+      <c r="M421" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -25319,15 +27424,20 @@
       </c>
       <c r="J422" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr">
+      <c r="L422" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L422" t="inlineStr">
+      <c r="M422" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -25379,15 +27489,20 @@
       </c>
       <c r="J423" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-27</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr">
+      <c r="L423" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L423" t="inlineStr">
+      <c r="M423" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -25439,15 +27554,20 @@
       </c>
       <c r="J424" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-27</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr">
+      <c r="L424" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L424" t="inlineStr">
+      <c r="M424" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -25499,15 +27619,20 @@
       </c>
       <c r="J425" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-27</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr">
+      <c r="L425" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L425" t="inlineStr">
+      <c r="M425" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -25559,15 +27684,20 @@
       </c>
       <c r="J426" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-28</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr">
+      <c r="L426" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L426" t="inlineStr">
+      <c r="M426" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -25619,15 +27749,20 @@
       </c>
       <c r="J427" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-28</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr">
+      <c r="L427" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L427" t="inlineStr">
+      <c r="M427" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -25679,15 +27814,20 @@
       </c>
       <c r="J428" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-28</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr">
+      <c r="L428" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L428" t="inlineStr">
+      <c r="M428" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -25739,15 +27879,20 @@
       </c>
       <c r="J429" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-28</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr">
+      <c r="L429" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L429" t="inlineStr">
+      <c r="M429" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -25799,15 +27944,20 @@
       </c>
       <c r="J430" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-28</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr">
+      <c r="L430" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L430" t="inlineStr">
+      <c r="M430" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -25859,15 +28009,20 @@
       </c>
       <c r="J431" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-28</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr">
+      <c r="L431" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L431" t="inlineStr">
+      <c r="M431" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -25919,15 +28074,20 @@
       </c>
       <c r="J432" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-28</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr">
+      <c r="L432" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L432" t="inlineStr">
+      <c r="M432" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -25979,15 +28139,20 @@
       </c>
       <c r="J433" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-28</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr">
+      <c r="L433" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L433" t="inlineStr">
+      <c r="M433" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -26039,15 +28204,20 @@
       </c>
       <c r="J434" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-28</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr">
+      <c r="L434" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L434" t="inlineStr">
+      <c r="M434" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -26099,15 +28269,20 @@
       </c>
       <c r="J435" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-28</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr">
+      <c r="L435" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L435" t="inlineStr">
+      <c r="M435" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -26159,15 +28334,20 @@
       </c>
       <c r="J436" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-28</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr">
+      <c r="L436" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L436" t="inlineStr">
+      <c r="M436" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -26219,15 +28399,20 @@
       </c>
       <c r="J437" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-28</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr">
+      <c r="L437" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L437" t="inlineStr">
+      <c r="M437" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -26279,15 +28464,20 @@
       </c>
       <c r="J438" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr">
+      <c r="L438" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L438" t="inlineStr">
+      <c r="M438" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -26339,15 +28529,20 @@
       </c>
       <c r="J439" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-18</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr">
+      <c r="L439" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L439" t="inlineStr">
+      <c r="M439" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -26399,15 +28594,20 @@
       </c>
       <c r="J440" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-18</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr">
+      <c r="L440" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L440" t="inlineStr">
+      <c r="M440" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -26459,15 +28659,20 @@
       </c>
       <c r="J441" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-18</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr">
+      <c r="L441" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L441" t="inlineStr">
+      <c r="M441" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -26519,15 +28724,20 @@
       </c>
       <c r="J442" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-18</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr">
+      <c r="L442" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L442" t="inlineStr">
+      <c r="M442" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -26579,15 +28789,20 @@
       </c>
       <c r="J443" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-18</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr">
+      <c r="L443" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L443" t="inlineStr">
+      <c r="M443" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -26639,15 +28854,20 @@
       </c>
       <c r="J444" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-18</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr">
+      <c r="L444" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L444" t="inlineStr">
+      <c r="M444" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -26699,15 +28919,20 @@
       </c>
       <c r="J445" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-18</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr">
+      <c r="L445" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L445" t="inlineStr">
+      <c r="M445" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -26759,15 +28984,20 @@
       </c>
       <c r="J446" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-18</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr">
+      <c r="L446" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L446" t="inlineStr">
+      <c r="M446" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -26819,15 +29049,20 @@
       </c>
       <c r="J447" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-18</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr">
+      <c r="L447" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L447" t="inlineStr">
+      <c r="M447" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -26879,15 +29114,20 @@
       </c>
       <c r="J448" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-18</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr">
+      <c r="L448" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L448" t="inlineStr">
+      <c r="M448" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -26939,15 +29179,20 @@
       </c>
       <c r="J449" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-18</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr">
+      <c r="L449" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L449" t="inlineStr">
+      <c r="M449" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -26999,15 +29244,20 @@
       </c>
       <c r="J450" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-19</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr">
+      <c r="L450" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L450" t="inlineStr">
+      <c r="M450" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -27059,15 +29309,20 @@
       </c>
       <c r="J451" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-20</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr">
+      <c r="L451" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L451" t="inlineStr">
+      <c r="M451" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -27119,15 +29374,20 @@
       </c>
       <c r="J452" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-25</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr">
+      <c r="L452" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L452" t="inlineStr">
+      <c r="M452" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -27179,21 +29439,26 @@
       </c>
       <c r="J453" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-09-03</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr">
+      <c r="L453" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L453" t="inlineStr">
+      <c r="M453" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L453"/>
+  <autoFilter ref="A1:M453"/>
 </worksheet>
 </file>
--- a/public/exports/29189803.xlsx
+++ b/public/exports/29189803.xlsx
@@ -9869,7 +9869,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029500</t>
+          <t xml:space="preserve">200029496</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029500</t>
+          <t xml:space="preserve">200029499</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029500</t>
+          <t xml:space="preserve">200029498</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029500</t>
+          <t xml:space="preserve">200029498</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029500</t>
+          <t xml:space="preserve">200029498</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029500</t>
+          <t xml:space="preserve">200029499</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029500</t>
+          <t xml:space="preserve">200029498</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029500</t>
+          <t xml:space="preserve">200029498</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582271</t>
+          <t xml:space="preserve">311582270</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -15849,7 +15849,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582271</t>
+          <t xml:space="preserve">311582270</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -16174,7 +16174,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594113</t>
+          <t xml:space="preserve">311594112</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -16239,7 +16239,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594113</t>
+          <t xml:space="preserve">311594112</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594113</t>
+          <t xml:space="preserve">311594112</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -22869,7 +22869,7 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t xml:space="preserve">311758142</t>
+          <t xml:space="preserve">311757995</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
@@ -23259,7 +23259,7 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759943</t>
+          <t xml:space="preserve">311759941</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759943</t>
+          <t xml:space="preserve">311759941</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
@@ -23389,7 +23389,7 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759943</t>
+          <t xml:space="preserve">311759941</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
@@ -24299,12 +24299,12 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t xml:space="preserve">311780699</t>
+          <t xml:space="preserve">311780599</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K374" t="inlineStr">
@@ -26184,7 +26184,7 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868109</t>
+          <t xml:space="preserve">311868068</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
@@ -26769,7 +26769,7 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874237</t>
+          <t xml:space="preserve">311874231</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
